--- a/sample-report/stakeholder-review-all.xlsx
+++ b/sample-report/stakeholder-review-all.xlsx
@@ -3235,7 +3235,19 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Confirmed absent after independent gap-check: no citable feature found; searches for InsightAppSec plus partner/open-banking/third-party-risk terms returned only generic industry TPRM content unrelated to Rapid7.</t>
+          <r>
+            <t xml:space="preserve">Confirmed absent after independent gap-check: no citable feature found; searches for InsightAppSec plus partner/open-banking/third-party-risk terms returned only generic industry TPRM content unrelated to Rapid7. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>rapid7.com/products/insightappsec</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (no partner-API-specific feature found there or elsewhere)</t>
+          </r>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -4217,12 +4229,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4594,7 +4607,16 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Only a 'Discovery scan' vs. 'Vulnerability scan' mode distinction was found; no explicit passive-mode/rate-limiting documentation located for WAS specifically -- a genuine research gap relative to other vendors scored so far.</t>
+          <r>
+            <t xml:space="preserve">Only a 'Discovery scan' vs. 'Vulnerability scan' mode distinction was found; no explicit passive-mode/rate-limiting documentation located for WAS specifically -- a genuine research gap relative to other vendors scored so far. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>cdn2.qualys.com/docs/qualys-was-getting-started-guide.pdf</t>
+          </r>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -4886,7 +4908,7 @@
             <t>ASP.NET</t>
           </r>
           <r>
-            <t xml:space="preserve"> WebForms/JSP/mainframe-gateway-specific claims found for WAS.</t>
+            <t xml:space="preserve"> WebForms/JSP/mainframe-gateway-specific claims found for WAS. Source: qualys.com/apps/web-app-scanning</t>
           </r>
         </is>
       </c>
@@ -4949,7 +4971,16 @@
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
-          <t>Confirmed weak after independent gap-check: 'Form Training' and Selenium/Browser-Recorder scripts enable crawling through multi-step workflows but no authorization-state-aware business-logic testing capability was found (nothing analogous to a privilege-escalation-diff test). A source explicitly states 'Standard DAST tools like Qualys WAS cannot validate business logic,' and this stands unrebutted.</t>
+          <r>
+            <t xml:space="preserve">Confirmed weak after independent gap-check: 'Form Training' and Selenium/Browser-Recorder scripts enable crawling through multi-step workflows but no authorization-state-aware business-logic testing capability was found (nothing analogous to a privilege-escalation-diff test). A source explicitly states 'Standard DAST tools like Qualys WAS cannot validate business logic,' and this stands unrebutted. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>getautonoma.com/blog/dast-tools</t>
+          </r>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
@@ -5233,7 +5264,16 @@
       </c>
       <c r="E15" s="18" t="inlineStr">
         <is>
-          <t>No independent benchmark or user-review data found specifically quantifying WAS's false-positive rate in either direction.</t>
+          <r>
+            <t xml:space="preserve">No independent benchmark or user-review data found specifically quantifying WAS's false-positive rate in either direction; the vendor's own product page makes no specific FP-rate claim either. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>qualys.com/apps/web-app-scanning</t>
+          </r>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -5295,7 +5335,19 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>TruRisk-based prioritization implied at the platform level; no WAS-specific instance-tailored remediation-guidance citation found distinct from generic vulnerability descriptions.</t>
+          <r>
+            <t xml:space="preserve">TruRisk-based prioritization implied at the platform level; no WAS-specific instance-tailored remediation-guidance citation found distinct from generic vulnerability descriptions. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.qualys.com/en/vmdr/latest/trurisk/truRisk_report.htm</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (platform-wide, not WAS-specific)</t>
+          </r>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -5357,7 +5409,16 @@
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>Confirmed weak after independent gap-check: no cross-scan learning or automated proof-of-concept replay found beyond manual ignore/exception marking and TruRisk's risk-prioritization scoring.</t>
+          <r>
+            <t xml:space="preserve">Confirmed weak after independent gap-check: no cross-scan learning or automated proof-of-concept replay found beyond manual ignore/exception marking and TruRisk's risk-prioritization scoring. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.qualys.com/en/was/latest/knowledgebase/ignore_vulnerability.htm</t>
+          </r>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
@@ -6082,7 +6143,16 @@
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>Vendor claims ML-optimized scan patterns reduce scan time by up to 80% on large applications -- self-reported, but a specific number.</t>
+          <r>
+            <t xml:space="preserve">Vendor claims ML-optimized scan patterns reduce scan time by up to 80% on large applications -- self-reported, but a specific number. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>qualys.com/apps/web-app-scanning</t>
+          </r>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -6366,7 +6436,16 @@
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>Confirmed absent after independent gap-check: no IDE plugin (VS Code, IntelliJ, Eclipse) or pre-commit tool found anywhere for WAS; only the CI/CD Jenkins plugin exists, which is pipeline integration, not local/IDE tooling.</t>
+          <r>
+            <t xml:space="preserve">Confirmed absent after independent gap-check: no IDE plugin (VS Code, IntelliJ, Eclipse) or pre-commit tool found anywhere for WAS; only the CI/CD Jenkins plugin exists, which is pipeline integration, not local/IDE tooling. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>plugins.jenkins.io/qualys-was</t>
+          </r>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -6499,7 +6578,16 @@
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>Confirmed absent after independent gap-check: Qualys's partner/vendor-asset content is under CSAM ('Import Third-Party Assets API') for general asset inventory, not a WAS-specific partner-API-differentiated scanning or risk-program-formatted output.</t>
+          <r>
+            <t xml:space="preserve">Confirmed absent after independent gap-check: Qualys's partner/vendor-asset content is under CSAM ('Import Third-Party Assets API') for general asset inventory, not a WAS-specific partner-API-differentiated scanning or risk-program-formatted output. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>qualys.com/faqs-resources-attack-surface-management</t>
+          </r>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
@@ -6635,7 +6723,16 @@
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
-          <t>Confirmed absent for WAS after independent gap-check: Qualys does have an 'Auto-Remediation' feature, but it is scoped to Policy Compliance (CAR scripts fixing infrastructure misconfigurations) and VMDR patch/ticket remediation -- not WAS, and not code-fix/PR generation.</t>
+          <r>
+            <t xml:space="preserve">Confirmed absent for WAS after independent gap-check: Qualys does have an 'Auto-Remediation' feature, but it is scoped to Policy Compliance (CAR scripts fixing infrastructure misconfigurations) and VMDR patch/ticket remediation -- not WAS, and not code-fix/PR generation. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>blog.qualys.com/product-tech/2023/04/03/augment-security-asset-tagging-with-custom-assessment-and-remediation-car</t>
+          </r>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -7235,28 +7332,37 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14367,7 +14473,16 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>OWASP Top 10 and OWASP API Security Top 10 mapping confirmed; no explicit PCI-DSS/GLBA/SOX/FFIEC/NYDFS regulatory-framework mapping found in DAST-specific documentation, though the platform broadly targets enterprise/regulated customers.</t>
+          <r>
+            <t xml:space="preserve">OWASP Top 10 and OWASP API Security Top 10 mapping confirmed; no explicit PCI-DSS/GLBA/SOX/FFIEC/NYDFS regulatory-framework mapping found in DAST-specific documentation, though the platform broadly targets enterprise/regulated customers. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>checkmarx.com/learn/integrating-dast-and-sast-into-devsecops-for-continuous-api-security</t>
+          </r>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -14429,7 +14544,16 @@
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>Proof-based scanning validates findings before flagging, and SAST-DAST correlation is cited to reduce noise -- but the vendor's own '89% noise reduction' figure applies to platform-wide ASPM correlation across all scanners, not a DAST-isolated false-positive rate, so it's cited here with that caveat rather than at face value.</t>
+          <r>
+            <t xml:space="preserve">Proof-based scanning validates findings before flagging, and SAST-DAST correlation is cited to reduce noise -- but the vendor's own '89% noise reduction' figure applies to platform-wide ASPM correlation across all scanners, not a DAST-isolated false-positive rate, so it's cited here with that caveat rather than at face value. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>checkmarx.com/blog/checkmarx-dast-for-the-ai-coding-era</t>
+          </r>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
@@ -16609,29 +16733,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18403,7 +18529,16 @@
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>AppScan on Cloud aggregates and correlates DAST, SAST, and IAST findings to provide proof of exploitability, prioritizing the most critical confirmed issues. Source: general platform documentation</t>
+          <r>
+            <t xml:space="preserve">AppScan on Cloud aggregates and correlates DAST, SAST, and IAST findings to provide proof of exploitability, prioritizing the most critical confirmed issues. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>hcl-software.com/appscan</t>
+          </r>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -18903,7 +19038,16 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>API-level discovery/inventory confirmed via the Salt Security partnership; not confirmed at the rubric's top tier of scanning public IP ranges/domains for rogue unmapped apps.</t>
+          <r>
+            <t xml:space="preserve">API-level discovery/inventory confirmed via the Salt Security partnership; not confirmed at the rubric's top tier of scanning public IP ranges/domains for rogue unmapped apps. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>hcl-software.com/appscan/products/api-security</t>
+          </r>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -19742,16 +19886,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample-report/stakeholder-review-all.xlsx
+++ b/sample-report/stakeholder-review-all.xlsx
@@ -1371,7 +1371,19 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>No credible independent benchmark found either direction after gap-check; the widely-circulated '94% false positive' figure (see false-positive-rate) is not a valid accuracy signal. Scored on general platform claims (signature-based detection, Universal Translator for modern frameworks) absent contrary evidence.</t>
+          <r>
+            <t xml:space="preserve">No credible independent benchmark found either direction after gap-check; the widely-circulated '94% false positive' figure (see false-positive-rate) is not a valid accuracy signal. Scored on general platform claims (signature-based detection, Universal Translator for modern frameworks) absent contrary evidence. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>peerspot.com/products/rapid7-insightappsec-reviews</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (general platform reviews checked; no credible independent accuracy benchmark found there)</t>
+          </r>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -4204,38 +4216,39 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4471,7 +4484,16 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Vendor claims a 96% detection rate via ML-optimized scan patterns -- self-reported, not independently benchmarked.</t>
+          <r>
+            <t xml:space="preserve">Vendor claims a 96% detection rate via ML-optimized scan patterns -- self-reported, not independently benchmarked. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>qualys.com/apps/web-app-scanning</t>
+          </r>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -7331,38 +7353,39 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7963,11 +7986,23 @@
         <v>6</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>No explicit passive-only/rate-limited safe-mode messaging found in public materials, though Proof-Based Scanning's non-destructive verification implies some inherent caution -- inferred, moderate confidence.</t>
+          <r>
+            <t xml:space="preserve">Revised up with real citations: a dedicated 'Scanning Production Environments' guide exists, passive security checks issue no extra HTTP requests, and scan speed is configurable across four tiers (Sequential/Slow/Moderate/Fast) specifically to handle rate-limited/production environments -- more concrete than initially found, though Invicti's own docs still caveat that active checks can be invasive even though non-destructive. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>invicti.com/support/scanning-production-environment</t>
+          </r>
+          <r>
+            <t>, docs.invicti.com/ip/target-scan-configuration</t>
+          </r>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -8248,7 +8283,19 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>SOAP API scanning explicitly supported; no legacy-framework-specific (ASP WebForms/JSP) accuracy claims found beyond general protocol coverage.</t>
+          <r>
+            <t xml:space="preserve">SOAP API scanning explicitly supported via WSDL schema parsing (file or URL), and </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>ASP.NET</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> applications are explicitly detected/supported including JS-heavy interfaces; no JSP-specific accuracy claims found beyond general protocol coverage. Source: invicti.com/soap-scanner, invicti.com/web-vulnerability-scanner/vulnerabilities/aspnet-identified</t>
+          </r>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -8810,7 +8857,16 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Licensed per-target (web app, API endpoint, or defined URL scope) across Standard/Premium/Enterprise tiers -- a clear, transparent axis, but Enterprise-tier pricing is fully customized/contact-sales, and approximate price ranges ($4k-6k Standard, $7k-12k Premium per target/year) come from third-party pricing aggregators, not Invicti's own published pricing page.</t>
+          <r>
+            <t xml:space="preserve">Licensed per-target (web app, API endpoint, or defined URL scope) across Standard/Premium/Enterprise tiers -- a clear, transparent axis -- but Enterprise-tier pricing is fully customized/contact-sales, and independent market data shows real-world deals commonly landing at $15,000-25,000+/year once RBAC/SCA/ASPM/on-prem/support are bundled in, well above the $4k-6k Standard-tier estimates quoted by third-party pricing aggregators (not Invicti's own published pricing page). Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>beaglesecurity.com/blog/article/invicti-pricing</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -8872,7 +8928,16 @@
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>Role-based access control explicitly marketed as part of its enterprise-focused platform, described as 'broader RBAC' relative to smaller competitors; audit-log capability not independently confirmed.</t>
+          <r>
+            <t xml:space="preserve">RBAC and Custom Roles are explicitly listed as Enterprise-edition features, marketed as 'broader RBAC' relative to smaller competitors; a dedicated audit-log capability was not independently confirmed in public materials. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>appsecsanta.com/invicti</t>
+          </r>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
@@ -8934,7 +8999,16 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Enterprise-platform positioning (dedicated account management, custom SLAs, on-prem deployment options) implies moderate setup complexity, more involved than a single docker-pull tool -- inferred from tier positioning, no explicit onboarding-time claim found.</t>
+          <r>
+            <t xml:space="preserve">Invicti's own recommended rollout plan allocates Days 1-10 of a 30-day implementation plan to onboarding, configuring, and prioritizing the first set of web apps/APIs -- moderate enterprise-platform setup complexity, not a minutes-to-first-scan tool, consistent with its enterprise positioning. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>invicti.com/support/invicti-quick-start-guide</t>
+          </r>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -9498,11 +9572,23 @@
         <v>2</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Enterprise tier implies scale (unlimited seats, custom SLAs, dedicated account management) but no explicit scan-speed or concurrency benchmark found in public materials -- inferred from tier positioning.</t>
+          <r>
+            <t xml:space="preserve">Revised up with real citations: configurable speed tiers (Sequential/Slow/Moderate/Fast, default Fast), plus a documented performance upgrade claiming up to 150% faster vulnerability discovery via dynamic resource allocation -- but independent commentary notes scalability challenges (resource consumption, longer scan times) when running many concurrent scanning agents across a large application portfolio. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>invicti.com/blog/web-security/netsparker-scan-performance-upgrades</t>
+          </r>
+          <r>
+            <t>, docs.invicti.com/ip/target-scan-configuration</t>
+          </r>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -9786,7 +9872,19 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>No dedicated vendor-risk-assessment output shaping for partner-facing APIs found in public materials -- inferred absence.</t>
+          <r>
+            <t xml:space="preserve">No dedicated vendor-risk-assessment output shaping for partner-facing APIs found in public materials -- inferred absence. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>invicti.com/solutions/financial-services</t>
+          </r>
+          <r>
+            <t>, docs.invicti.com/ie-is/manage-api-inventory (API Inventory filters only by source/scan date/target/type, no partner-risk categorization)</t>
+          </r>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -9915,11 +10013,20 @@
         <v>1</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>SIEM integration mentioned generally as part of its broader toolchain integrations, but no specific named platforms (e.g. Splunk, Elasticsearch) confirmed in public materials.</t>
+          <r>
+            <t xml:space="preserve">Revised up with a real citation: a dedicated, unified Invicti Enterprise add-on for Splunk (supporting both Splunk Enterprise on-prem and Splunk Cloud) is published on Splunkbase -- a confirmed native SIEM integration, though no QRadar or Microsoft Sentinel integration was found. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.invicti.com/ie-is/invicti-enterprise-addon-splunk</t>
+          </r>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -10588,29 +10695,37 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10846,7 +10961,19 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>No specific detection-rate benchmark found in public materials; inferred from general enterprise reputation as an established SAST/DAST/SCA platform, not a specific accuracy claim.</t>
+          <r>
+            <t xml:space="preserve">No specific independent detection-rate benchmark found for Veracode's DAST specifically; scored from general enterprise-platform positioning and market recognition (a 9x Gartner Magic Quadrant Leader for Application Security Testing) rather than a cited accuracy number. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>veracode.com/products/dynamic-analysis-dast</t>
+          </r>
+          <r>
+            <t>, securityscientist.net/blog/12-questions-and-answers-about-veracode-dast</t>
+          </r>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -12364,7 +12491,19 @@
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>No dedicated financial-data-pattern (account/routing number, card PAN) detection capability found -- inferred absence.</t>
+          <r>
+            <t xml:space="preserve">No dedicated financial-data-pattern (account/routing number, card PAN) detection capability found -- inferred absence. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.veracode.com/r/c_review_cwe</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (only generic sensitive-data-exposure CWEs found, CWE-200/201/359 family; no dedicated financial-pattern detector for PANs/routing numbers/SSNs)</t>
+          </r>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -12422,11 +12561,20 @@
         <v>2</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>No dedicated proof-of-exploit/safe-re-exploitation engine found (unlike Invicti's Proof-Based Scanning); DAST's dynamic/behavioral nature gives some inherent evidence over static pattern matching, but no explicit confirmation-engine claim.</t>
+          <r>
+            <t xml:space="preserve">Revised up with a real citation: clicking a finding in Veracode DAST Essentials surfaces the exact payload used for the exploit, and findings can be independently replicated via a generated curl request -- a concrete proof-of-exploit mechanism comparable to other proof-based scanners, not just an inherent dynamic-testing advantage over static pattern matching. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>veracode.com/blog/getting-started-guide-veracode-dast-essentials</t>
+          </r>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -12775,7 +12923,19 @@
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>Community integration tooling (Veracode-Community-Projects) exists for automation/glue, but no detection-rule-authoring DSL comparable to ZAP's Zest or Nuclei's YAML templates found.</t>
+          <r>
+            <t xml:space="preserve">Community integration tooling (Veracode-Community-Projects) exists for automation/glue, but no detection-rule-authoring DSL comparable to ZAP's Zest or Nuclei's YAML templates found. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.veracode.com/r/c_sc_policies_custom</t>
+          </r>
+          <r>
+            <t>, docs.veracode.com/r/Create_Custom_Rules_for_Agent_Based_Scanning (custom rules found are for SCA agent-based scanning license/component policy controls, not new DAST detection signatures)</t>
+          </r>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -12837,7 +12997,19 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>No confirmed native SIEM/SOAR integration found in research -- explicitly a research gap rather than a confirmed absence; only community Slack-webhook-redirect tooling for SCA agent results was found.</t>
+          <r>
+            <t xml:space="preserve">No confirmed native SIEM/SOAR integration found in research -- explicitly a research gap rather than a confirmed absence; only community Slack-webhook-redirect tooling for SCA agent results was found. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.veracode.com/r/Veracode_Integrations</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (official integrations page lists Jira/Bugzilla/RSA Archer/Imperva/CI-CD/IDE tools, no native Splunk/QRadar/Sentinel/XSOAR), splunkbase.splunk.com/app/7277 ('Veracode Splunk Bridge' is third-party/community-built, not Veracode-authored)</t>
+          </r>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -12899,7 +13071,19 @@
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>No dedicated vendor-risk-assessment output shaping for partner-facing APIs found -- inferred absence.</t>
+          <r>
+            <t xml:space="preserve">No dedicated vendor-risk-assessment output shaping for partner-facing APIs found -- inferred absence. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>veracode.com/security/third-party-risk-assessment</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (Veracode's 'third-party risk' products, SCA/VAST, address risk from vendors' code coming in, not risk of your APIs facing partners -- opposite direction from the rubric)</t>
+          </r>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
@@ -13640,33 +13824,39 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13902,7 +14092,19 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Comprehensive OWASP Top 10 and OWASP API Top 10 coverage claimed, plus business-logic-aware testing -- but no independently published benchmark/ground-truth accuracy score found. Paper confidence, inferred from platform positioning rather than a cited third-party benchmark.</t>
+          <r>
+            <t xml:space="preserve">Comprehensive OWASP Top 10 and OWASP API Top 10 coverage claimed, plus business-logic-aware testing -- but no independently published benchmark/ground-truth accuracy score found. Paper confidence, inferred from platform positioning rather than a cited third-party benchmark. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>checkmarx.com/checkmarx-dast</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (vendor's own general accuracy/coverage claim, not an independent benchmark)</t>
+          </r>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -16726,38 +16928,39 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20133,7 +20336,16 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>VENDOR CLAIM, not independently verified. HawkScan runs real attacks against the live app; dedicated Intelligent Business Logic Testing feature specifically targets authorization/logic flaws -- notable vs ZAP/Nuclei. All from StackHawk's own marketing.</t>
+          <r>
+            <t xml:space="preserve">VENDOR CLAIM, not independently verified. HawkScan runs real attacks against the live app; dedicated Intelligent Business Logic Testing feature specifically targets authorization/logic flaws -- notable vs ZAP/Nuclei. Documented engineering-level detection refinements (e.g. correctly distinguishing true/false boolean-blind-SQLi condition responses) show ongoing tuning, but all from StackHawk's own materials. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.stackhawk.com/changelog.html</t>
+          </r>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -20269,7 +20481,16 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>JWT, OAuth flows, most 3rd-party providers directly configurable in the stackhawk YAML config without custom scripts -- strong, low-friction, well-documented.</t>
+          <r>
+            <t xml:space="preserve">JSON/form-based auth plus 3rd-party OAuth 2.0 identity providers (Auth0, Okta, Firebase, KeyCloak) directly configurable in the YAML config, with external token injection available for custom scenarios outside the scanner -- strong, low-friction, well-documented. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.stackhawk.com/getting-started/auth-scan.html</t>
+          </r>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -20331,7 +20552,19 @@
       </c>
       <c r="E7" s="18" t="inlineStr">
         <is>
-          <t>Cloud-only execution (config-as-code + cloud backend, Tier 2 per dast-onboard-tool's tiering); no on-prem or configurable data-residency option found.</t>
+          <r>
+            <t xml:space="preserve">Cloud-only execution (config-as-code + cloud backend, Tier 2 per dast-onboard-tool's tiering); no on-prem or configurable data-residency option found. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>appsecsanta.com</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (independent review states StackHawk is SaaS-only with no on-prem/air-gapped option, contrasted against Invicti which offers on-prem)</t>
+          </r>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
@@ -20464,7 +20697,16 @@
       </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>Core value prop -- YAML config-as-code, deliberately CI-native exit-code design: exit 42 for findings-threshold-reached vs exit 1 for scan failure, cleanly distinguishable.</t>
+          <r>
+            <t xml:space="preserve">Core value prop -- YAML config-as-code, deliberately CI-native exit-code design: exit 42 specifically when the configured failure threshold is reached (distinguishable from exit 1 for an actual scan error). Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.stackhawk.com/getting-started</t>
+          </r>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
@@ -20526,7 +20768,16 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Explicit SOAP support alongside REST/GraphQL/gRPC (SOAP is often legacy-adjacent); no legacy-framework-specific (older Microsoft web forms, JSP) testing confirmed.</t>
+          <r>
+            <t xml:space="preserve">Explicit SOAP support alongside REST/GraphQL/gRPC (SOAP is often legacy-adjacent); no legacy-framework-specific (older Microsoft web forms, JSP) testing confirmed. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>stackhawk.com/solutions/dast</t>
+          </r>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -20807,7 +21058,16 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>VENDOR CLAIM. Runtime testing against live app (not code patterns) reduces FPs per their own materials -- directionally credible but unverified independently.</t>
+          <r>
+            <t xml:space="preserve">VENDOR CLAIM. Runtime testing against the live app (not code patterns) reduces FPs per their own materials; documented specific improvements (stripping query/form parameter values to reduce SQLi false positives on input-validated apps) are more concrete than generic marketing, though still first-party and not independently verified. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.stackhawk.com/changelog.html</t>
+          </r>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -20869,7 +21129,16 @@
       </c>
       <c r="E15" s="18" t="inlineStr">
         <is>
-          <t>Remediation guidance written in the target language with code-level context, not generic jargon.</t>
+          <r>
+            <t xml:space="preserve">Remediation guidance is written in the target language with code-level, framework-tailored context, not generic security jargon -- fixes can be reviewed and applied directly in the editor. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>stackhawk.com/blog/how-does-stackhawk-work</t>
+          </r>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -20931,7 +21200,16 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Real, documented finding-lifecycle workflow (mark as Assigned/Risk Accepted/False Positive, tied to Jira) -- best-documented of the three candidates here.</t>
+          <r>
+            <t xml:space="preserve">Real, documented finding-lifecycle workflow (mark as Assigned/Risk Accepted/False Positive, tied to Jira issues) -- best-documented of the three original candidates on this criterion. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.stackhawk.com/integrations/workflows/jira</t>
+          </r>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -21063,11 +21341,20 @@
         <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Real finding-lifecycle workflow (Assigned/Risk Accepted/False Positive) persists manual triage decisions across scans -- but no documented automated PoC-generation or ML-driven historical learning.</t>
+          <r>
+            <t xml:space="preserve">Real finding-lifecycle workflow (Assigned/Risk Accepted/False Positive) persists manual triage decisions across scans, and documented engineering-level false-positive-reduction improvements (e.g. boolean-blind-SQLi refinement) show ongoing algorithmic tuning -- but no documented automated PoC-generation or cross-scan ML-driven learning engine. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.stackhawk.com/changelog.html</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -21125,11 +21412,23 @@
         <v>3</v>
       </c>
       <c r="D19" s="17" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>Publicly documented per-application/target-based tiered SaaS pricing at smaller tiers (transparent, footprint-aligned), but enterprise-scale tiers move to custom/contact-sales pricing -- less transparent at the scale a Fortune 500 buyer would operate at.</t>
+          <r>
+            <t xml:space="preserve">Corrected and revised up: pricing is actually contributor-based (not per-application/target as originally stated) -- a real published starting price ($42/contributor/month, Pro at $49/contributor/month with a 20-contributor minimum), which independent commentary notes provides more predictable costs as testing volume increases than per-scan/per-app models. Enterprise-scale tiers still move to custom/contact-sales pricing. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>stackhawk.com/pricing</t>
+          </r>
+          <r>
+            <t>, beaglesecurity.com/blog/article/stackhawk-pricing</t>
+          </r>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
@@ -21187,11 +21486,23 @@
         <v>3</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>'Activity history and audit logging' mentioned as an enterprise feature; fine-grained RBAC not explicitly confirmed.</t>
+          <r>
+            <t xml:space="preserve">Revised up with a real citation: StackHawk Enterprise explicitly includes role-based permissions, activity history &amp; audit log (tracking org membership changes, scans kicked off, findings triaged), and SSO/SAML -- direct confirmation of fine-grained RBAC that the original pass couldn't find. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>stackhawk.com/pricing</t>
+          </r>
+          <r>
+            <t>, docs.stackhawk.com/web-app/sso-saml-integration.html</t>
+          </r>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -21253,7 +21564,16 @@
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>Three-line YAML minimum config, onboarding wizard -- fast, but requires SaaS signup/API key, a qualitatively different friction than a docker pull.</t>
+          <r>
+            <t xml:space="preserve">Confirmed minimum config is a genuine three-line YAML file (applicationId/env/host); an onboarding wizard builds a complete config in a few clicks -- fast, but requires SaaS signup/API key, a qualitatively different friction than a docker pull. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.stackhawk.com/getting-started/quickstart</t>
+          </r>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
@@ -21315,7 +21635,16 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Built on ZAP's underlying scan engine (inherits baseline capability), but StackHawk's product positioning/workflow (HawkScan configs driven by OpenAPI/GraphQL specs) is API-first -- multi-page traditional crawling isn't a marketed strength.</t>
+          <r>
+            <t xml:space="preserve">Originally built on ZAP's underlying scan engine, but HawkScan Test Engine (HSTE) is now a complete re-engineering of that foundation for CI/CD (container-first, API-first architecture); Selenium-based crawling handles more complex structures than simple traditional HTTP crawling, but StackHawk's positioning/workflow (specs-driven configs) is API-first -- multi-page traditional crawling isn't a marketed strength. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>appsecsanta.com/stackhawk-vs-zap</t>
+          </r>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -21525,7 +21854,16 @@
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>HawkScan runs real dynamic tests against the live running application by design (not static pattern matching), inherently closer to proof-of-exploit validation than a signature-only tool.</t>
+          <r>
+            <t xml:space="preserve">HawkScan runs real dynamic tests against the live running application by design (not static pattern matching), and each finding carries a documented confidence-level field (High/Medium/Low) -- inherently closer to proof-of-exploit validation than a signature-only tool, though Low-confidence results are explicitly flagged as needing independent confirmation. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.stackhawk.com/hawkscan/viewing-scan-results</t>
+          </r>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -21583,11 +21921,20 @@
         <v>2</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Markets itself as an 'AppSec Intelligence Platform,' implying dashboard/trend views, though an explicit remediation-velocity trend view isn't independently confirmed.</t>
+          <r>
+            <t xml:space="preserve">Revised up with real citations: the 'Application Security Oversight' product tracks every vulnerability from discovery through validated remediation, provides a real-time risk-posture dashboard, and generates board-level metrics showing whether risk is being reduced over time, not just scan-activity counts -- more concrete than the original 'implied by platform positioning' framing. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>stackhawk.com/product/oversight</t>
+          </r>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -21649,7 +21996,19 @@
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>Direct, first-party Jira/Slack/PR-comment integrations -- stronger than ZAP's plugin-based story, comparable to Nuclei's SARIF.</t>
+          <r>
+            <t xml:space="preserve">Direct, first-party Jira Cloud integration (auto-creates issues, comments on linked issues, supports any issue type) and a Slack app (scan-start notifications plus a findings summary by risk on completion) -- stronger than ZAP's plugin-based story, comparable to Nuclei's SARIF/tracker integrations. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.stackhawk.com/integrations/workflows/jira</t>
+          </r>
+          <r>
+            <t>, slack.com/marketplace/A0114L5HGP5-stackhawk</t>
+          </r>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -21711,7 +22070,16 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Cloud-backed execution built for per-PR CI/CD gating implies genuine scale across many apps, not limited by a single self-hosted instance.</t>
+          <r>
+            <t xml:space="preserve">Unlimited applications/scans with no concurrency restrictions as usage scales per the published pricing model; the scanner runs within the customer's own infrastructure/CI pipeline (eliminating internet latency), and scans complete in minutes, which is what makes per-PR gating practical. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>stackhawk.com/blog/running-stackhawk-in-cicd</t>
+          </r>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -22140,7 +22508,19 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>No dedicated vendor-risk-assessment output shaping found for partner-facing APIs specifically.</t>
+          <r>
+            <t xml:space="preserve">No dedicated vendor-risk-assessment output shaping found for partner-facing APIs specifically. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>stackhawk.com/solutions/stackhawk-for-financial-sector</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (only generic 'sensitive financial data' marketing language; no open-banking/partner-API-specific scanning mode or vendor-risk-formatted output)</t>
+          </r>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -22202,7 +22582,19 @@
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
-          <t>Delivers findings into PR comments and auto-generates a reproduction cURL command -- doesn't generate a fix diff or open a PR automatically.</t>
+          <r>
+            <t xml:space="preserve">Delivers findings into PR comments and auto-generates a reproduction cURL command -- doesn't generate a fix diff or open a PR automatically. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.stackhawk.com/integrations/workflows/github/github-pr-checks</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (only posts commit statuses and PR comment summaries linking to findings, no auto-generated fix diff or auto-opened PR), stackhawk.com/blog/github-copilot-secure-code (Copilot Agent Skill's Fix step is user-invoked Copilot chat editing, not an autonomous PR)</t>
+          </r>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -22801,20 +23193,39 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23112,7 +23523,16 @@
       </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>Form/script-based auth and HTTP session management are solid; SSO/OAuth/MFA flows handleable via custom Zest scripts but require manual scripting, not native support.</t>
+          <r>
+            <t xml:space="preserve">Native authentication methods (browser-based, client script, form-based, JSON-based, auto-detect) plus session management (header/cookie-based, auto-detect); Client Script (Zest) authentication automates complex/custom login flows since there's no dedicated native SSO/OAuth/MFA auth type -- solid but requires manual scripting for anything beyond the built-in methods. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>deepwiki.com/zaproxy/zap-extensions/2.3-authentication-and-session-management</t>
+          </r>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
@@ -23316,7 +23736,19 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>First-class docker CLI scripts (the zap-full-scan script, etc.), YAML Automation Framework, clear exit codes, machine-readable JSON/XML output -- this project's own CI pipeline uses it directly.</t>
+          <r>
+            <t xml:space="preserve">First-class docker automation via the </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>zap-full-scan.py</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> script (ghcr.io/zaproxy/zaproxy:stable image) plus the newer YAML-based Automation Framework covering contexts, authentication, spider, active scan, and report generation as discrete jobs -- this project's own CI pipeline uses it directly. Source: zaproxy.org/docs/docker</t>
+          </r>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -23378,7 +23810,16 @@
       </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>Fully self-hostable by nature (docker/desktop/CLI) -- all scan data and traffic stay wherever you run it, inherently on-prem/air-gap-capable since it isn't a SaaS product at all.</t>
+          <r>
+            <t xml:space="preserve">Runs entirely self-hosted -- desktop app, the official docker image, or CLI -- with no SaaS/cloud-backend component at all, so all scan data and traffic stay wherever it's run, inherently on-prem/air-gap-capable by nature rather than by a configured deployment option. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>zaproxy.org/docs/docker</t>
+          </r>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
@@ -23440,7 +23881,19 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Protocol-agnostic HTTP(S) proxy/scanner since 2010; traditional server-rendered/legacy web tech was its original design target before SPA-crawling was added.</t>
+          <r>
+            <t xml:space="preserve">Founded in 2010 as a fork of Paros Proxy, ZAP was originally a general-purpose HTTP(S) intercepting proxy/scanner predating SPA-era tooling, making it inherently protocol/framework-agnostic for classic server-rendered legacy applications; SPA-specific crawling (AJAX Spider) was added later as an add-on. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>en.wikipedia.org/wiki/ZAP_(software</t>
+          </r>
+          <r>
+            <t>)</t>
+          </r>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -23573,7 +24026,19 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>No exception/risk-acceptance workflow or audit trail for finding lifecycle -- a scan-and-report tool, not a vulnerability management platform.</t>
+          <r>
+            <t xml:space="preserve">No exception/risk-acceptance workflow or audit trail for finding lifecycle -- a scan-and-report tool, not a vulnerability management platform. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>zaproxy.org/docs</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (ZAP itself has no lifecycle workflow beyond a flat alert list; the only related evidence found, Checkmarx One's triage states/audit trail, is that separate paid platform's feature)</t>
+          </r>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -23771,7 +24236,16 @@
       </c>
       <c r="E15" s="18" t="inlineStr">
         <is>
-          <t>AJAX Spider + traditional spider do JS-bundle/common-path heuristic discovery; no dedicated deprecated/versioned-endpoint detection engine.</t>
+          <r>
+            <t xml:space="preserve">AJAX Spider (built on the Crawljax engine) executes JavaScript to discover new paths/API routes in SPA/AJAX applications; no dedicated deprecated/versioned-endpoint detection engine confirmed beyond that JS-execution-based path discovery. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>zaproxy.org/docs/desktop/addons/ajax-spider</t>
+          </r>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -23833,7 +24307,19 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Every alert includes a description, solution text, and references -- generic per-vulnerability-class advice, not tailored to the specific instance/tech stack.</t>
+          <r>
+            <t xml:space="preserve">Every alert includes a Description, a Solution, and References -- static text that is identical for every instance of the same alert type, since ZAP has no access to source code to tailor guidance to the specific instance/tech stack. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>zaproxy.org/docs/desktop/start/features/alerts</t>
+          </r>
+          <r>
+            <t>, zaproxy.org/docs/alerts</t>
+          </r>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -23895,7 +24381,19 @@
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>No built-in RBAC or audit logging; single-user tool by design, relies on OS/CI-level access control.</t>
+          <r>
+            <t xml:space="preserve">No built-in RBAC or audit logging; single-user tool by design, relies on OS/CI-level access control. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>zaproxy.org/docs</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (ZAP itself, run locally/via CLI, has no user/role concept at all; the only related evidence found, Checkmarx One's 5 predefined RBAC roles, is that separate paid platform's feature)</t>
+          </r>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
@@ -23957,7 +24455,16 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Alert Filters let you globally suppress a specific rule/pattern once flagged, persisting across future scans -- static rule-based suppression, not adaptive learning or PoC-based auto-confirmation.</t>
+          <r>
+            <t xml:space="preserve">Alert Filters can change alerts matching specific criteria to a 'False Positive' confidence level, and this persists across future scans -- static, rule-based suppression configured by the user, not adaptive/ML learning or automated proof-of-concept-based re-confirmation. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>zaproxy.org/docs/desktop/addons/alert-filters</t>
+          </r>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -24019,7 +24526,16 @@
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>Fully open-source (Apache 2.0); zero cost regardless of usage scale -- the most predictable possible model.</t>
+          <r>
+            <t xml:space="preserve">Fully open-source under the Apache License 2.0, confirmed by ZAP's own legal notice; zero cost regardless of usage scale -- the most predictable possible licensing model. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>github.com/zaproxy/zaproxy/blob/main/LEGALNOTICE.md</t>
+          </r>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
@@ -24081,7 +24597,19 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Free, official docker images, first useful scan achievable in minutes with sensible defaults -- confirmed by this project's own live-verification run.</t>
+          <r>
+            <t>Free, official docker images (</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>ghcr.io/zaproxy/zaproxy</t>
+          </r>
+          <r>
+            <t>) enable a first useful scan in minutes with sensible defaults -- independently confirmed by this project's own live-verification run during the initial dogfood session. Source: zaproxy.org/docs/docker</t>
+          </r>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -24143,7 +24671,19 @@
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>ZAP's traditional Spider is one of its oldest, most mature features -- built specifically for multi-page, session-stateful crawling before SPAs existed, with well-documented forms/session handling.</t>
+          <r>
+            <t xml:space="preserve">ZAP's traditional Spider predates the AJAX Spider add-on (added later specifically for SPAs), reflecting its original design as a classic multi-page, session-stateful crawler from its 2010 founding as a Paros Proxy fork. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>en.wikipedia.org/wiki/ZAP_(software</t>
+          </r>
+          <r>
+            <t>)</t>
+          </r>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
@@ -24276,7 +24816,19 @@
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>Produces per-scan reports only; no cross-scan executive trend dashboard.</t>
+          <r>
+            <t xml:space="preserve">Produces per-scan reports only; no cross-scan executive trend dashboard. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>zaproxy.org/docs</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (no historical/trend view exists in ZAP itself; the only related evidence found, Checkmarx One's Executive Overview Dashboard, is a separate paid platform's feature, not available in OSS ZAP)</t>
+          </r>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
@@ -24483,7 +25035,16 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>DefectDojo (a named example ASPM platform) ships a native, documented ZAP-report parser/importer -- a real first-party connector on the ASPM side, not just generic export.</t>
+          <r>
+            <t xml:space="preserve">DefectDojo, a named example ASPM platform, ships a dedicated, documented ZAP scan-report parser/importer as one of its supported import types -- a real first-party connector on the ASPM side, not just generic export. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>ironflower.nl/blog/defectdojo/defectdojo.html</t>
+          </r>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -24545,7 +25106,16 @@
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>Active scan rules attach real evidence (matched payload/response snippet) for many findings, but not a formalized/systematic proof-of-exploit engine across all rule types.</t>
+          <r>
+            <t xml:space="preserve">Active scan alerts attach real evidence (the matched payload/response snippet) per finding instance, but this is not a formalized, systematic proof-of-exploit/re-exploitation engine spanning all rule types. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>zaproxy.org/docs/desktop/start/features/alerts</t>
+          </r>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -24607,7 +25177,19 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>HTML/XML/JSON/Markdown report generation; community plugins for Jira/Slack exist but aren't first-party/polished.</t>
+          <r>
+            <t xml:space="preserve">Native HTML, XML, and JSON report formats (JSON commonly used for pipeline/external-tool integration); a community-built (not first-party) add-on exports alerts as Jira issues. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>zaproxy.org/docs/desktop/addons/report-generation</t>
+          </r>
+          <r>
+            <t>, kasunbalasooriya.medium.com/an-add-on-for-owasp-zap-to-export-alerts-of-a-web-application-as-issues-to-jira</t>
+          </r>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -24665,11 +25247,20 @@
         <v>2</v>
       </c>
       <c r="D29" s="17" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>Generic PII Disclosure passive rule likely catches common patterns (SSN, card-like numbers), but no dedicated account/routing-number-specific detection.</t>
+          <r>
+            <t xml:space="preserve">Revised up with a real citation: the PII Disclosure passive rule (alert 10062) explicitly detects credit-card-like numbers validated via a Luhn checksum plus a Bank Identification Number (BIN) list lookup, and SSN-like patterns -- a more rigorous, validated mechanism than a bare regex match. No dedicated bank-routing/account-number-specific detection was confirmed. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>zaproxy.org/docs/alerts/10062</t>
+          </r>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
@@ -24731,7 +25322,19 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Not an attack-surface-management tool; requires a manually-provided target.</t>
+          <r>
+            <t xml:space="preserve">Not an attack-surface-management tool; requires a manually-provided target. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>github.com/zaproxy/zaproxy/wiki/RelatedProjects</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (OWASP Amass is a separate, unrelated OWASP project, only listed as a 'Related Project' on ZAP's wiki, not an integration)</t>
+          </r>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -24867,7 +25470,19 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Possible via third-party bridging tools (e.g. Flame, forwarding ZAP output to Splunk) -- not a native ZAP capability.</t>
+          <r>
+            <t xml:space="preserve">Possible via third-party bridging tools (e.g. Flame, forwarding ZAP output to Splunk) -- not a native ZAP capability. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>zaproxy.org/docs</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (ZAP itself only outputs JSON/XML/HTML/Markdown reports, no CEF/syslog or native SIEM/SOAR connector)</t>
+          </r>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -25000,7 +25615,19 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Highly extensible -- custom active/passive scan rules via Zest/Python/JS/Groovy scripting, large add-on marketplace.</t>
+          <r>
+            <t xml:space="preserve">Scripting engine supports any JSR223-compatible language (Zest, JavaScript, Groovy, Python, Ruby); dedicated Active Scan Rules and Passive Scan Rules add-ons let custom detection logic run as part of a normal scan, backed by a large community add-on marketplace. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>zaproxy.org/docs/desktop/addons/active-scan-rules</t>
+          </r>
+          <r>
+            <t>, zaproxy.org/docs/desktop/addons/passive-scan-rules</t>
+          </r>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -25062,7 +25689,19 @@
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
-          <t>No auto-remediation or auto-PR capability -- it's a scanner, not a code-fixing tool.</t>
+          <r>
+            <t xml:space="preserve">No auto-remediation or auto-PR capability -- it's a scanner, not a code-fixing tool. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>github.com/zaproxy/action-full-scan</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> (ZAP's own official GitHub Action only opens/updates/closes a GitHub issue, no diff, no PR)</t>
+          </r>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -25658,16 +26297,37 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26036,7 +26696,16 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Rate-limiting flags exist and most templates are non-destructive by nature (matching, not exploiting), but no dedicated safe-mode branding/formal guarantee like ZAP's.</t>
+          <r>
+            <t xml:space="preserve">Rate-limit (-rl/-rlm) and concurrency (-c/-pc) flags plus a 'template-spray' scan strategy that spreads load across many targets instead of hammering one -- real configurability for sensitive environments, but templates are match-based by default rather than a formally branded 'safe mode' like ZAP's. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.projectdiscovery.io/opensource/nuclei/mass-scanning-cli</t>
+          </r>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -26598,7 +27267,16 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Normalized CWE metadata and CVE/CVSS classification across templates (recent improvement); no financial-services-specific (GLBA/SOX/FFIEC/NYDFS) mapping out of the box.</t>
+          <r>
+            <t xml:space="preserve">Classification metadata (cvss-metrics, cvss-score, cve-id, cwe-id) is being actively normalized across templates, including a recent effort to normalize CWE-ID metadata across HTTP exposure/misconfiguration templates; no financial-services-specific (GLBA/SOX/FFIEC/NYDFS) mapping out of the box. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>github.com/projectdiscovery/nuclei-templates/blob/main/TEMPLATE-CREATION-GUIDE.md</t>
+          </r>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -26660,7 +27338,19 @@
       </c>
       <c r="E15" s="18" t="inlineStr">
         <is>
-          <t>Exposure/technology-fingerprint templates do heuristic path-guessing, similar depth to ZAP; no deprecated/versioned-endpoint-aware discovery engine.</t>
+          <r>
+            <t xml:space="preserve">Exposure/technology-fingerprint templates check for known paths (e.g. </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>robots.txt</t>
+          </r>
+          <r>
+            <t>) as heuristic fingerprinting; the template catalog is actively pruned of false-positive/deprecated-service templates, but there's no dedicated deprecated/versioned-API-endpoint-aware discovery engine. Source: projectdiscovery.io/blog/nuclei-templates-april-2026</t>
+          </r>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -26722,7 +27412,16 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Templates include name/description/references, but quality is inconsistent across 11,000+ community-contributed templates.</t>
+          <r>
+            <t xml:space="preserve">Template info block includes name/description/reference/severity/classification (CVSS/CWE/CVE) fields, but quality is inconsistent across 12,000+ community-contributed templates and not tailored to the specific instance/tech stack. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.projectdiscovery.io/templates/structure</t>
+          </r>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -26932,7 +27631,16 @@
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>Core engine is free/MIT -- maximally predictable at zero cost. ProjectDiscovery's cloud ASM platform (where advanced features live) uses enterprise/contact-sales pricing without public per-asset rate transparency.</t>
+          <r>
+            <t xml:space="preserve">Core engine plus all 12,000+ community templates are MIT-licensed and free -- maximally predictable at zero cost. ProjectDiscovery Cloud (where advanced ASM/team features live) uses enterprise/contact-sales pricing without public per-asset rate transparency. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>github.com/projectdiscovery/nuclei</t>
+          </r>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
@@ -26990,11 +27698,20 @@
         <v>3</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Cloud platform supports team members (up to 10 free), but fine-grained RBAC and an audit log are not confirmed.</t>
+          <r>
+            <t xml:space="preserve">Revised up with a real citation: ProjectDiscovery Cloud provides granular RBAC with defined roles, enterprise SSO integration, and comprehensive audit logs tracking who ran a scan, acknowledged a vulnerability, or changed a setting, with timestamps. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>projectdiscovery.io/blog/projectdiscovery-achieves-soc-2-type-2-certification</t>
+          </r>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -27056,7 +27773,16 @@
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>Single static Go binary, go install or docker, -update-templates auto-fetches the library -- genuinely lower friction than ZAP's Java/docker footprint.</t>
+          <r>
+            <t xml:space="preserve">Single static Go binary installable via 'go install', a prebuilt binary download, or docker pull; '-update-templates' (or automatic first-run fetch) downloads the full community template library. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.projectdiscovery.io/opensource/nuclei/install</t>
+          </r>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
@@ -27114,11 +27840,23 @@
         <v>3</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Cloud platform is explicitly described as SOC 2 compliant; ISO 27001 certification or a published third-party pentest summary not confirmed.</t>
+          <r>
+            <t xml:space="preserve">Revised up with a real citation: ProjectDiscovery achieved SOC 2 Type 2 certification (AICPA SSAE 18 standard), confirmed via a dedicated announcement, plus a public Trust Center (SafeBase-powered); ISO 27001 certification still not confirmed. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>projectdiscovery.io/blog/projectdiscovery-achieves-soc-2-type-2-certification</t>
+          </r>
+          <r>
+            <t>, security.projectdiscovery.io</t>
+          </r>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -27328,7 +28066,16 @@
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>A template match is itself a precise, specific assertion about the condition tested -- arguably inherently more confirmed than a generic payload-based finding -- though not universally accompanied by attached response evidence.</t>
+          <r>
+            <t xml:space="preserve">A template match is itself a precise, specific assertion (a matcher checking a string/regex/status-code against the actual response) -- arguably inherently more confirmed than a generic payload-based finding -- though not universally accompanied by explicit exploit-proof evidence beyond the match itself. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.projectdiscovery.io/templates/structure</t>
+          </r>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -27386,11 +28133,20 @@
         <v>2</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Cloud platform likely has some dashboard view given its continuous-monitoring nature, but an explicit remediation-velocity/risk-reduction trend view isn't confirmed.</t>
+          <r>
+            <t xml:space="preserve">Revised up with a real citation: ProjectDiscovery Cloud has built-in compliance/executive report generation, but an explicit remediation-velocity/risk-reduction-over-time trend view specifically isn't confirmed. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>projectdiscovery.io/blog/projectdiscovery-achieves-soc-2-type-2-certification</t>
+          </r>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -27452,7 +28208,19 @@
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>JSON/JSONL/SARIF output -- SARIF integrates natively with GitHub's code-scanning security tab, a stronger integration story than ZAP's plugin-based approach.</t>
+          <r>
+            <t xml:space="preserve">Native JSON, JSONL (-jsonl), and SARIF (-sarif-export) output; SARIF integrates natively with GitHub/GitLab code-scanning security tabs via the official nuclei-action. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.github.com/en/code-security/code-scanning/integrating-with-code-scanning/sarif-support-for-code-scanning</t>
+          </r>
+          <r>
+            <t>, github.com/projectdiscovery/nuclei-action</t>
+          </r>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -27514,7 +28282,19 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>OSS tool is fast/concurrent by design; ProjectDiscovery's cloud platform explicitly markets continuous scanning 'at scale' across many assets.</t>
+          <r>
+            <t xml:space="preserve">Configurable rate-limit/concurrency/payload-concurrency flags support fast, parallel execution by design; ProjectDiscovery's cloud platform explicitly markets continuous scanning across an org's full exposure surface with daily auto-refresh. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.projectdiscovery.io/opensource/nuclei/mass-scanning-cli</t>
+          </r>
+          <r>
+            <t>, projectdiscovery.io/blog/pdcp-0-8-8</t>
+          </r>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -27576,7 +28356,19 @@
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>Native, documented integrations to Jira/GitHub/GitLab with built-in deduplication preventing duplicate tickets -- more official than ZAP's community-maintained add-ons.</t>
+          <r>
+            <t xml:space="preserve">Native Tracker integrations for GitHub, GitLab, Jira, and Linear with built-in deduplication (persisted locally in </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>reporting-db.json</t>
+          </r>
+          <r>
+            <t>) that prevents duplicate tickets and can close issues automatically once a subsequent clean scan shows the vulnerability resolved -- more official than ZAP's community-maintained add-ons. Source: github.com/projectdiscovery/nuclei/blob/main/DESIGN.md</t>
+          </r>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
@@ -27712,7 +28504,19 @@
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>Cloud platform's attack-surface-management angle is about discovering your own exposed assets, not partner/third-party-integration risk assessment specifically.</t>
+          <r>
+            <t xml:space="preserve">Cloud platform's attack-surface-management angle is about discovering your own exposed assets, not partner/third-party-integration risk assessment specifically. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>projectdiscovery.featurebase.app/p/api-security</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> ('API Security' appears on ProjectDiscovery's public roadmap, not yet shipped)</t>
+          </r>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -27845,7 +28649,16 @@
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>The entire tool is custom rules -- a simple YAML DSL explicitly designed for community/user-authored templates, no vendor involvement needed.</t>
+          <r>
+            <t xml:space="preserve">The entire engine is built around a simple YAML DSL explicitly designed for community/user-authored detection templates -- no vendor involvement needed to add new detection logic. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>docs.projectdiscovery.io/templates/structure</t>
+          </r>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
@@ -27907,7 +28720,16 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Native, documented integrations to Splunk and Elasticsearch.</t>
+          <r>
+            <t xml:space="preserve">Native Exporter integrations for Splunk and Elasticsearch (plus MongoDB). Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>deepwiki.com/projectdiscovery/nuclei/6-output-and-reporting</t>
+          </r>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -28043,7 +28865,16 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Cloud platform does continuous asset/change monitoring (new hosts/endpoints detected automatically) -- incremental at the asset-discovery level, not confirmed at the application-code level.</t>
+          <r>
+            <t xml:space="preserve">ProjectDiscovery Cloud continuously monitors internet-exposed assets, automatically discovering new hosts/endpoints and alerting on attack-surface changes -- incremental at the asset-discovery/exposure level, not confirmed at the application-code/endpoint-content level the rubric describes. Source: </t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="000563C1"/>
+              <u val="single"/>
+            </rPr>
+            <t>projectdiscovery.io/blog/the-new-way-to-discover-your-exposure</t>
+          </r>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -28569,19 +29400,36 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
